--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486752_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486752_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6013</v>
+        <v>6.7529</v>
       </c>
       <c r="E2" t="n">
-        <v>9.483599999999999</v>
+        <v>10.0076</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.8823</v>
+        <v>-3.2548</v>
       </c>
       <c r="G2" t="n">
         <v>14.6711</v>
@@ -610,13 +610,13 @@
         <v>2.8962</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.813</v>
+        <v>-2.6615</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3796</v>
+        <v>-0.8555</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.4335</v>
+        <v>-1.806</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2021</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2432</v>
+        <v>3.9136</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1214</v>
+        <v>4.8663</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8781</v>
+        <v>-0.9526</v>
       </c>
       <c r="G3" t="n">
         <v>2.438</v>
@@ -688,13 +688,13 @@
         <v>1.1585</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3805</v>
+        <v>-0.7101</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3032</v>
+        <v>0.0481</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6837</v>
+        <v>-0.7582</v>
       </c>
       <c r="V3" t="n">
         <v>1.0273</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H. CARRON GRILLO</t>
+          <t>M. PIZARRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3796</v>
+        <v>-0.3004</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3407</v>
+        <v>1.2603</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-1.5607</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7007</v>
+        <v>0.3497</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6691</v>
+        <v>-0.1725</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0316</v>
+        <v>0.5222</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0177</v>
+        <v>1.3776</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0207</v>
+        <v>0.7242</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0384</v>
+        <v>0.6534</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-1.0278</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6898</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0068</v>
+        <v>-0.1311</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0275</v>
+        <v>0.0482</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3584</v>
+        <v>-0.1173</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3309</v>
+        <v>0.1655</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2856</v>
+        <v>-1.4707</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2856</v>
+        <v>-1.4707</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. PIZARRO</t>
+          <t>H. CARRON GRILLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5031</v>
+        <v>-0.614</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1569</v>
+        <v>-0.0178</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.66</v>
+        <v>-0.5962</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3497</v>
+        <v>-0.7007</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1725</v>
+        <v>-0.6691</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5222</v>
+        <v>-0.0316</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3776</v>
+        <v>-0.0177</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7242</v>
+        <v>0.0207</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6534</v>
+        <v>-0.0384</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0278</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-0.6898</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1311</v>
+        <v>0.0068</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7723</v>
+        <v>0.5792</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7723</v>
+        <v>0.5792</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1545</v>
+        <v>-0.2069</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2207</v>
+        <v>-0.0001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.2068</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.4707</v>
+        <v>-0.2856</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4707</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5103</v>
+        <v>-1.4552</v>
       </c>
       <c r="E6" t="n">
-        <v>1.206</v>
+        <v>1.2612</v>
       </c>
       <c r="F6" t="n">
         <v>-2.7164</v>
@@ -922,10 +922,10 @@
         <v>1.9308</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.2065</v>
+        <v>-2.1513</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4693</v>
+        <v>-0.4142</v>
       </c>
       <c r="U6" t="n">
         <v>-1.7371</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.3346</v>
+        <v>-3.2009</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4913</v>
+        <v>-2.3327</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8433</v>
+        <v>-0.8682</v>
       </c>
       <c r="G7" t="n">
         <v>-3.5884</v>
@@ -1000,13 +1000,13 @@
         <v>0.7723</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.175</v>
+        <v>-1.0413</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.607</v>
+        <v>-0.4484</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.5929</v>
       </c>
       <c r="V7" t="n">
         <v>0.6565</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ROLDAN GAYOSO</t>
+          <t>M. VILLANUEVA CUBELO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.1191</v>
+        <v>-3.9277</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7403</v>
+        <v>-3.0526</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3788</v>
+        <v>-0.8751</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.9345</v>
+        <v>-0.1334</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.4417</v>
+        <v>-0.2692</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4928</v>
+        <v>0.1357</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9472</v>
+        <v>1.9787</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.303</v>
+        <v>2.0079</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6442</v>
+        <v>-0.0293</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9873</v>
+        <v>-2.1121</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.1387</v>
+        <v>-2.2771</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1514</v>
+        <v>0.165</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5792</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>-5.02</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5446</v>
+        <v>2.8962</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4783</v>
+        <v>-2.9236</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8277</v>
+        <v>-0.9107</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6506</v>
+        <v>-2.013</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2856</v>
+        <v>1.2533</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.8995</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2856</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. VILLANUEVA CUBELO</t>
+          <t>M. ROLDAN GAYOSO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.6449</v>
+        <v>-4.0543</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5215</v>
+        <v>-2.5265</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1234</v>
+        <v>-1.5278</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1334</v>
+        <v>-2.9345</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2692</v>
+        <v>-2.4417</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1357</v>
+        <v>-0.4928</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9787</v>
+        <v>-0.9472</v>
       </c>
       <c r="K9" t="n">
-        <v>2.0079</v>
+        <v>-0.303</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0293</v>
+        <v>-0.6442</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1121</v>
+        <v>-1.9873</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.2771</v>
+        <v>-2.1387</v>
       </c>
       <c r="O9" t="n">
-        <v>0.165</v>
+        <v>0.1514</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.1239</v>
+        <v>0.5792</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.02</v>
+        <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8962</v>
+        <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.6408</v>
+        <v>-1.4135</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3796</v>
+        <v>-0.6139</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.2613</v>
+        <v>-0.7995</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2533</v>
+        <v>-0.2856</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8995</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3538</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.0298</v>
+        <v>-4.9223</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1195</v>
+        <v>-1.9126</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9103</v>
+        <v>-3.0096</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9065</v>
@@ -1234,13 +1234,13 @@
         <v>1.1585</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3073</v>
+        <v>-1.1998</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5518</v>
+        <v>-0.345</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.8548</v>
       </c>
       <c r="V10" t="n">
         <v>-1.816</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.3666</v>
+        <v>-8.6836</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.3727</v>
+        <v>-5.9381</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9939</v>
+        <v>-2.7456</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6768</v>
@@ -1312,13 +1312,13 @@
         <v>2.7031</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.7307</v>
+        <v>-3.0478</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0558</v>
+        <v>-0.6211</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.675</v>
+        <v>-2.4266</v>
       </c>
       <c r="V11" t="n">
         <v>-1.573</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-17.0435</v>
+        <v>-16.4919</v>
       </c>
       <c r="E12" t="n">
-        <v>1.063299999999998</v>
+        <v>1.615099999999997</v>
       </c>
       <c r="F12" t="n">
-        <v>-18.1068</v>
+        <v>-18.107</v>
       </c>
       <c r="G12" t="n">
         <v>4.964599999999999</v>
@@ -1390,10 +1390,10 @@
         <v>16.4117</v>
       </c>
       <c r="S12" t="n">
-        <v>-15.8591</v>
+        <v>-15.3076</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.829899999999999</v>
+        <v>-4.2781</v>
       </c>
       <c r="U12" t="n">
         <v>-11.0294</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8568</v>
+        <v>4.7189</v>
       </c>
       <c r="E13" t="n">
-        <v>6.9682</v>
+        <v>6.4511</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1114</v>
+        <v>-1.7322</v>
       </c>
       <c r="G13" t="n">
         <v>-1.2813</v>
@@ -1468,13 +1468,13 @@
         <v>1.7377</v>
       </c>
       <c r="S13" t="n">
-        <v>3.0342</v>
+        <v>1.8963</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5993</v>
+        <v>1.0822</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4349</v>
+        <v>0.8141</v>
       </c>
       <c r="V13" t="n">
         <v>4.2969</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. CASTELANOS POLA</t>
+          <t>J. BOONYASITH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7331</v>
+        <v>3.7552</v>
       </c>
       <c r="E14" t="n">
-        <v>1.774</v>
+        <v>4.8797</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9591</v>
+        <v>-1.1245</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5832000000000001</v>
+        <v>2.286</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1447</v>
+        <v>0.1587</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7279</v>
+        <v>2.1272</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5151</v>
+        <v>5.267</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1316</v>
+        <v>2.0907</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3835</v>
+        <v>3.1763</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9319</v>
+        <v>-2.981</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2763</v>
+        <v>-1.9319</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-1.049</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1239</v>
+        <v>-2.8962</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-4.827</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1239</v>
+        <v>1.9308</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3389</v>
+        <v>1.91</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5718</v>
+        <v>1.4131</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7671</v>
+        <v>0.4969</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.3129</v>
+        <v>2.4554</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.3129</v>
+        <v>3.0266</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.684</v>
+        <v>3.6717</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0725</v>
+        <v>1.7622</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6115</v>
+        <v>1.9095</v>
       </c>
       <c r="G15" t="n">
         <v>1.1908</v>
@@ -1624,13 +1624,13 @@
         <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>1.605</v>
+        <v>1.5927</v>
       </c>
       <c r="T15" t="n">
-        <v>1.627</v>
+        <v>1.3167</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.022</v>
+        <v>0.276</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6565</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. KELLIER</t>
+          <t>A. CASTELANOS POLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8409</v>
+        <v>3.6006</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0387</v>
+        <v>1.774</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1978</v>
+        <v>1.8267</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.0707</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7671</v>
+        <v>-0.1447</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.8378</v>
+        <v>0.7279</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3312</v>
+        <v>1.5151</v>
       </c>
       <c r="K16" t="n">
-        <v>5.0438</v>
+        <v>0.1316</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.7127</v>
+        <v>1.3835</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.4019</v>
+        <v>-0.9319</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.2768</v>
+        <v>-0.2763</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.1251</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5792</v>
+        <v>2.1239</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.2823</v>
+        <v>2.1239</v>
       </c>
       <c r="S16" t="n">
-        <v>4.1481</v>
+        <v>2.2065</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2263</v>
+        <v>1.5718</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9218</v>
+        <v>0.6347</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3428</v>
+        <v>-1.3129</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3428</v>
+        <v>-1.3129</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. BOONYASITH</t>
+          <t>N. CEBRIAN HERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6836</v>
+        <v>2.0361</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1557</v>
+        <v>-0.7045</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4721</v>
+        <v>2.7406</v>
       </c>
       <c r="G17" t="n">
-        <v>2.286</v>
+        <v>-0.409</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1587</v>
+        <v>2.6067</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1272</v>
+        <v>-3.0157</v>
       </c>
       <c r="J17" t="n">
-        <v>5.267</v>
+        <v>-0.1661</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0907</v>
+        <v>3.1593</v>
       </c>
       <c r="L17" t="n">
-        <v>3.1763</v>
+        <v>-3.3253</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.981</v>
+        <v>-0.2429</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9319</v>
+        <v>-0.5525</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.049</v>
+        <v>0.3096</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.8962</v>
+        <v>0.5792</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.827</v>
+        <v>-1.9308</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9308</v>
+        <v>2.51</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8384</v>
+        <v>2.1514</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6891</v>
+        <v>1.3924</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1493</v>
+        <v>0.7591</v>
       </c>
       <c r="V17" t="n">
-        <v>2.4554</v>
+        <v>-0.2856</v>
       </c>
       <c r="W17" t="n">
-        <v>3.0266</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5712</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. CEBRIAN HERNANDEZ</t>
+          <t>J. KELLIER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.613</v>
+        <v>1.8853</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1524</v>
+        <v>2.1079</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7654</v>
+        <v>-0.2226</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.409</v>
+        <v>-2.0707</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6067</v>
+        <v>2.7671</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.0157</v>
+        <v>-4.8378</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1661</v>
+        <v>2.3312</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1593</v>
+        <v>5.0438</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.3253</v>
+        <v>-2.7127</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2429</v>
+        <v>-4.4019</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5525</v>
+        <v>-2.2768</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3096</v>
+        <v>-2.1251</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5792</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9308</v>
+        <v>-3.8616</v>
       </c>
       <c r="R18" t="n">
-        <v>2.51</v>
+        <v>3.2823</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7282999999999999</v>
+        <v>3.1925</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0555</v>
+        <v>2.2955</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7839</v>
+        <v>0.8969</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2856</v>
+        <v>1.3428</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.3428</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.313</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0345</v>
+        <v>-0.4482</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3475</v>
+        <v>0.3724</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5309</v>
@@ -1936,13 +1936,13 @@
         <v>0.1931</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6509</v>
+        <v>0.262</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6343</v>
+        <v>0.2206</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SOLA ARGEMI</t>
+          <t>F. NAVARRO ANTON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.011</v>
+        <v>-0.2482</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1206</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1096</v>
+        <v>0.3724</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.427</v>
+        <v>-0.5309</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6893</v>
+        <v>0.1586</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.7377</v>
+        <v>-0.6895</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5678</v>
+        <v>-0.6688</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1736</v>
+        <v>0.0207</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6058</v>
+        <v>-0.6895</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.9948</v>
+        <v>0.1379</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.8629</v>
+        <v>0.1379</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.1319</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.8962</v>
+        <v>0.1931</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5153</v>
+        <v>0.0896</v>
       </c>
       <c r="T20" t="n">
-        <v>2.0129</v>
+        <v>0.0482</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5024</v>
+        <v>0.0414</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.0426</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4707</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. NAVARRO ANTON</t>
+          <t>J. SOLA ARGEMI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3764</v>
+        <v>-0.3323</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.724</v>
+        <v>1.6035</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3475</v>
+        <v>-1.9357</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5309</v>
+        <v>-3.427</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1586</v>
+        <v>-0.6893</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6895</v>
+        <v>-2.7377</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6688</v>
+        <v>0.5678</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0207</v>
+        <v>1.1736</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6895</v>
+        <v>-0.6058</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1379</v>
+        <v>-3.9948</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1379</v>
+        <v>-1.8629</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-2.1319</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1931</v>
+        <v>2.8962</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0386</v>
+        <v>2.172</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0552</v>
+        <v>1.4958</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0166</v>
+        <v>0.6762</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.0426</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.4707</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3154</v>
+        <v>-1.9266</v>
       </c>
       <c r="E22" t="n">
-        <v>0.888</v>
+        <v>1.3017</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.2034</v>
+        <v>-3.2283</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7748</v>
@@ -2170,13 +2170,13 @@
         <v>0.9654</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0386</v>
+        <v>0.4275</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2207</v>
+        <v>0.193</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2594</v>
+        <v>0.2345</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6138</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>17.0436</v>
+        <v>17.0849</v>
       </c>
       <c r="E23" t="n">
-        <v>18.1068</v>
+        <v>18.1069</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.063299999999999</v>
+        <v>-1.021699999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-4.9646</v>
       </c>
       <c r="H23" t="n">
-        <v>4.485</v>
+        <v>4.484999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-9.4498</v>
+        <v>-9.449799999999998</v>
       </c>
       <c r="J23" t="n">
         <v>15.3216</v>
@@ -2227,7 +2227,7 @@
         <v>14.8352</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4865000000000004</v>
+        <v>0.4864999999999999</v>
       </c>
       <c r="M23" t="n">
         <v>-20.2862</v>
@@ -2239,7 +2239,7 @@
         <v>-9.936199999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9654000000000003</v>
+        <v>0.9654</v>
       </c>
       <c r="Q23" t="n">
         <v>-16.4118</v>
@@ -2248,13 +2248,13 @@
         <v>17.3771</v>
       </c>
       <c r="S23" t="n">
-        <v>15.8591</v>
+        <v>15.9005</v>
       </c>
       <c r="T23" t="n">
         <v>11.0293</v>
       </c>
       <c r="U23" t="n">
-        <v>4.830000000000001</v>
+        <v>4.8712</v>
       </c>
       <c r="V23" t="n">
         <v>5.183699999999999</v>
